--- a/address_data.xlsx
+++ b/address_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\users\user\Desktop\py\07.找完整地址\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31B684D7-E9FA-4DA7-B150-1FC2006C2E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E2A96C5-6812-4782-A2E6-803894A7EC00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -403,8 +403,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="45.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -425,16 +431,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
